--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q10_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0287062145404279</v>
+        <v>0.01595933867655232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0287062145404279</v>
+        <v>0.01595933867655232</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01601802198180555</v>
+        <v>0.009068878022050786</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02848586721799337</v>
+        <v>0.0157792313249901</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02848586721799337</v>
+        <v>0.0157792313249901</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01492377967925484</v>
+        <v>0.008661384692003766</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.02789228047286679</v>
+        <v>0.01537191592100733</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02789228047286679</v>
+        <v>0.01537191592100733</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01398747410166306</v>
+        <v>0.008325686688681569</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02698332376420686</v>
+        <v>0.01478625334355417</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02698332376420686</v>
+        <v>0.01478625334355417</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01313281382499712</v>
+        <v>0.008021572829663232</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02606417119374065</v>
+        <v>0.01421095974586744</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02606417119374065</v>
+        <v>0.01421095974586744</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01213805039958012</v>
+        <v>0.007644441588461662</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02534590159936444</v>
+        <v>0.0137727868341304</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02534590159936444</v>
+        <v>0.0137727868341304</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01095220574087019</v>
+        <v>0.007177695834940076</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02492199306575269</v>
+        <v>0.01352390246714252</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02492199306575269</v>
+        <v>0.01352390246714252</v>
       </c>
       <c r="D8" t="n">
-        <v>0.009594563177646969</v>
+        <v>0.006657939339570706</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02489357499030992</v>
+        <v>0.01351804082632888</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02489357499030992</v>
+        <v>0.01351804082632888</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008155468860123204</v>
+        <v>0.006109101087333096</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02516248347749523</v>
+        <v>0.01369765564401836</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02516248347749523</v>
+        <v>0.01369765564401836</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006892476532334608</v>
+        <v>0.005723387505141835</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.02638412445085532</v>
+        <v>0.01442208287810191</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02638412445085532</v>
+        <v>0.01442208287810191</v>
       </c>
       <c r="D11" t="n">
-        <v>0.006066333600331579</v>
+        <v>0.005545617897873004</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02814941094972109</v>
+        <v>0.01546164340500133</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02814941094972109</v>
+        <v>0.01546164340500133</v>
       </c>
       <c r="D12" t="n">
-        <v>0.005787188300586207</v>
+        <v>0.005595503837066281</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.03069940447900434</v>
+        <v>0.01694762440725519</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03069940447900434</v>
+        <v>0.01694762440725519</v>
       </c>
       <c r="D13" t="n">
-        <v>0.005955811815218503</v>
+        <v>0.005836854078286545</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03423314049129303</v>
+        <v>0.01898914622127615</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03423314049129303</v>
+        <v>0.01898914622127615</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006367977536306107</v>
+        <v>0.006193518846073237</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03844155396222541</v>
+        <v>0.02140956362163621</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03844155396222541</v>
+        <v>0.02140956362163621</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006893175827002304</v>
+        <v>0.00665452559399394</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04339255259522876</v>
+        <v>0.02424253061116739</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04339255259522876</v>
+        <v>0.02424253061116739</v>
       </c>
       <c r="D16" t="n">
-        <v>0.007578617796276437</v>
+        <v>0.007241820191488064</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.04891276104040325</v>
+        <v>0.0273849993571068</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04891276104040325</v>
+        <v>0.0273849993571068</v>
       </c>
       <c r="D17" t="n">
-        <v>0.008710683366250076</v>
+        <v>0.008131833567510139</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.05479677889307941</v>
+        <v>0.03071428152652449</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05479677889307941</v>
+        <v>0.03071428152652449</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01066116102962013</v>
+        <v>0.009423816561976692</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0610606190813846</v>
+        <v>0.03423313763494915</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0610606190813846</v>
+        <v>0.03423313763494915</v>
       </c>
       <c r="D19" t="n">
-        <v>0.01325551648178742</v>
+        <v>0.01109788241048761</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06762482432661397</v>
+        <v>0.03789332108769071</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06762482432661397</v>
+        <v>0.03789332108769071</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01583737160090049</v>
+        <v>0.01288707146669263</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.07415008500955689</v>
+        <v>0.041503038025284</v>
       </c>
       <c r="C21" t="n">
-        <v>0.07415008500955689</v>
+        <v>0.041503038025284</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01763273815138723</v>
+        <v>0.01435675576045771</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.08048663135293249</v>
+        <v>0.04498281181454376</v>
       </c>
       <c r="C22" t="n">
-        <v>0.08048663135293249</v>
+        <v>0.04498281181454376</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01788130661038514</v>
+        <v>0.01518532274827942</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.08669729069102752</v>
+        <v>0.04837731411149189</v>
       </c>
       <c r="C23" t="n">
-        <v>0.08669729069102752</v>
+        <v>0.04837731411149189</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01636507003876282</v>
+        <v>0.01529207879599629</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.09323368458538946</v>
+        <v>0.05195110109443638</v>
       </c>
       <c r="C24" t="n">
-        <v>0.09323368458538946</v>
+        <v>0.05195110109443638</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01357162450106886</v>
+        <v>0.0150675216707578</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1004131837525232</v>
+        <v>0.05589831865945073</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1004131837525232</v>
+        <v>0.05589831865945073</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01027126117467344</v>
+        <v>0.01502914609906011</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1085301164990181</v>
+        <v>0.0603932293381036</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1085301164990181</v>
+        <v>0.0603932293381036</v>
       </c>
       <c r="D26" t="n">
-        <v>0.007488958552387126</v>
+        <v>0.01551382107476978</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1173691656707027</v>
+        <v>0.0653165107891116</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1173691656707027</v>
+        <v>0.0653165107891116</v>
       </c>
       <c r="D27" t="n">
-        <v>0.006363532244896308</v>
+        <v>0.01655193762835909</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.126833512092926</v>
+        <v>0.07061839506885123</v>
       </c>
       <c r="C28" t="n">
-        <v>0.126833512092926</v>
+        <v>0.07061839506885123</v>
       </c>
       <c r="D28" t="n">
-        <v>0.007139638989546746</v>
+        <v>0.01806512272171997</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1365454695210897</v>
+        <v>0.07608076754603163</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1365454695210897</v>
+        <v>0.07608076754603163</v>
       </c>
       <c r="D29" t="n">
-        <v>0.008613443019145536</v>
+        <v>0.0197851115890311</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1460792992033559</v>
+        <v>0.08145636143090679</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1460792992033559</v>
+        <v>0.08145636143090679</v>
       </c>
       <c r="D30" t="n">
-        <v>0.009964956957801762</v>
+        <v>0.02153243528914112</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1551882310806023</v>
+        <v>0.08660146577669488</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1551882310806023</v>
+        <v>0.08660146577669488</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01100221317815316</v>
+        <v>0.02321067357205618</v>
       </c>
     </row>
   </sheetData>
